--- a/Mau_Dang_Ky_Xe_Import.xlsx
+++ b/Mau_Dang_Ky_Xe_Import.xlsx
@@ -1,41 +1,209 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Vibe Coding\DTK\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0660337A-CD8D-41E8-B79B-10666FB5529F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="DanhSachXeDangKy" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="59">
+  <si>
+    <t>VehicleType</t>
+  </si>
+  <si>
+    <t>CargoDirection</t>
+  </si>
+  <si>
+    <t>LicensePlate</t>
+  </si>
+  <si>
+    <t>ContainerNo</t>
+  </si>
+  <si>
+    <t>WeightKg</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>DriverName</t>
+  </si>
+  <si>
+    <t>DriverPhone</t>
+  </si>
+  <si>
+    <t>RegistrationDate</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>CONTAINER</t>
+  </si>
+  <si>
+    <t>IMPORT</t>
+  </si>
+  <si>
+    <t>MSCU1234567</t>
+  </si>
+  <si>
+    <t>ABC LOGISTICS</t>
+  </si>
+  <si>
+    <t>Nguyễn Văn An</t>
+  </si>
+  <si>
+    <t>0903123456</t>
+  </si>
+  <si>
+    <t>Hàng linh kiện điện tử nhập khẩu cảng Cát Lái</t>
+  </si>
+  <si>
+    <t>EXPORT</t>
+  </si>
+  <si>
+    <t>TEMU9988776</t>
+  </si>
+  <si>
+    <t>TÂN CẢNG LOGISTICS</t>
+  </si>
+  <si>
+    <t>Trần Văn Bình</t>
+  </si>
+  <si>
+    <t>0918765432</t>
+  </si>
+  <si>
+    <t>Container hàng may mặc xuất khẩu đi Mỹ</t>
+  </si>
+  <si>
+    <t>TRUCK</t>
+  </si>
+  <si>
+    <t>29C-678.90</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>VẬN TẢI THÀNH PHÁT</t>
+  </si>
+  <si>
+    <t>Lê Hoàng Cường</t>
+  </si>
+  <si>
+    <t>0988654321</t>
+  </si>
+  <si>
+    <t>Xe tải 6.5 tấn chở nông sản xuất khẩu</t>
+  </si>
+  <si>
+    <t>60C-888.99</t>
+  </si>
+  <si>
+    <t>ĐỒNG NAI TRANS</t>
+  </si>
+  <si>
+    <t>Phạm Quốc Dũng</t>
+  </si>
+  <si>
+    <t>0977112233</t>
+  </si>
+  <si>
+    <t>Xe tải nặng 12.5 tấn nhận hàng sắt thép</t>
+  </si>
+  <si>
+    <t>15C-345.67</t>
+  </si>
+  <si>
+    <t>ONEU5544332</t>
+  </si>
+  <si>
+    <t>HẢI PHÒNG MARITIME</t>
+  </si>
+  <si>
+    <t>Vũ Đức Em</t>
+  </si>
+  <si>
+    <t>0933445566</t>
+  </si>
+  <si>
+    <t>Cont đông lạnh nhập khẩu</t>
+  </si>
+  <si>
+    <t>61C-456.78</t>
+  </si>
+  <si>
+    <t>BÌNH DƯƠNG EXPRESS</t>
+  </si>
+  <si>
+    <t>Đỗ Hùng Giang</t>
+  </si>
+  <si>
+    <t>0966778899</t>
+  </si>
+  <si>
+    <t>Xe tải nhẹ 5.2 tấn chở bao bì carton</t>
+  </si>
+  <si>
+    <t>51D-789.01</t>
+  </si>
+  <si>
+    <t>CMAU8877665</t>
+  </si>
+  <si>
+    <t>SAI GON SHIPLOG</t>
+  </si>
+  <si>
+    <t>Bùi Văn Hùng</t>
+  </si>
+  <si>
+    <t>0944556677</t>
+  </si>
+  <si>
+    <t>Cont hạt điều xuất khẩu châu Âu</t>
+  </si>
+  <si>
+    <t>72C-234.56</t>
+  </si>
+  <si>
+    <t>VŨNG TÀU TRANSPORT</t>
+  </si>
+  <si>
+    <t>Ngô Đình Khôi</t>
+  </si>
+  <si>
+    <t>0922334455</t>
+  </si>
+  <si>
+    <t>Xe tải 3 chân 15 tấn xuất hàng vật tư</t>
+  </si>
+  <si>
+    <t>51C-288.55</t>
+  </si>
+  <si>
+    <t>50H-299.88</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -64,14 +232,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -396,312 +573,312 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="16.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" customWidth="1"/>
-    <col min="7" max="7" width="20.83203125" customWidth="1"/>
-    <col min="8" max="8" width="15.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
-    <col min="10" max="10" width="38.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.875" customWidth="1"/>
+    <col min="2" max="4" width="16.875" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="25.875" customWidth="1"/>
+    <col min="7" max="7" width="20.875" customWidth="1"/>
+    <col min="8" max="8" width="15.875" customWidth="1"/>
+    <col min="9" max="9" width="18.875" customWidth="1"/>
+    <col min="10" max="10" width="38.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>VehicleType</v>
-      </c>
-      <c r="B1" t="str">
-        <v>CargoDirection</v>
-      </c>
-      <c r="C1" t="str">
-        <v>LicensePlate</v>
-      </c>
-      <c r="D1" t="str">
-        <v>ContainerNo</v>
-      </c>
-      <c r="E1" t="str">
-        <v>WeightKg</v>
-      </c>
-      <c r="F1" t="str">
-        <v>Company</v>
-      </c>
-      <c r="G1" t="str">
-        <v>DriverName</v>
-      </c>
-      <c r="H1" t="str">
-        <v>DriverPhone</v>
-      </c>
-      <c r="I1" t="str">
-        <v>RegistrationDate</v>
-      </c>
-      <c r="J1" t="str">
-        <v>Note</v>
+    <row r="1" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>CONTAINER</v>
-      </c>
-      <c r="B2" t="str">
-        <v>IMPORT</v>
-      </c>
-      <c r="C2" t="str">
-        <v>51C-123.45</v>
-      </c>
-      <c r="D2" t="str">
-        <v>MSCU1234567</v>
+    <row r="2" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
       </c>
       <c r="E2">
         <v>28500</v>
       </c>
-      <c r="F2" t="str">
-        <v>ABC LOGISTICS</v>
-      </c>
-      <c r="G2" t="str">
-        <v>Nguyễn Văn An</v>
-      </c>
-      <c r="H2" t="str">
-        <v>0903123456</v>
-      </c>
-      <c r="I2" t="str">
-        <v>08/10/2026</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Hàng linh kiện điện tử nhập khẩu cảng Cát Lái</v>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="1">
+        <v>46304</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>CONTAINER</v>
-      </c>
-      <c r="B3" t="str">
-        <v>EXPORT</v>
-      </c>
-      <c r="C3" t="str">
-        <v>50H-987.65</v>
-      </c>
-      <c r="D3" t="str">
-        <v>TEMU9988776</v>
+    <row r="3" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
       </c>
       <c r="E3">
         <v>30200</v>
       </c>
-      <c r="F3" t="str">
-        <v>TÂN CẢNG LOGISTICS</v>
-      </c>
-      <c r="G3" t="str">
-        <v>Trần Văn Bình</v>
-      </c>
-      <c r="H3" t="str">
-        <v>0918765432</v>
-      </c>
-      <c r="I3" t="str">
-        <v>08/10/2026</v>
-      </c>
-      <c r="J3" t="str">
-        <v>Container hàng may mặc xuất khẩu đi Mỹ</v>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" t="s">
+        <v>21</v>
+      </c>
+      <c r="I3" s="1">
+        <v>46304</v>
+      </c>
+      <c r="J3" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>TRUCK</v>
-      </c>
-      <c r="B4" t="str">
-        <v>EXPORT</v>
-      </c>
-      <c r="C4" t="str">
-        <v>29C-678.90</v>
-      </c>
-      <c r="D4" t="str">
-        <v/>
+    <row r="4" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" t="s">
+        <v>25</v>
       </c>
       <c r="E4">
         <v>6500</v>
       </c>
-      <c r="F4" t="str">
-        <v>VẬN TẢI THÀNH PHÁT</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Lê Hoàng Cường</v>
-      </c>
-      <c r="H4" t="str">
-        <v>0988654321</v>
-      </c>
-      <c r="I4" t="str">
-        <v>08/10/2026</v>
-      </c>
-      <c r="J4" t="str">
-        <v>Xe tải 6.5 tấn chở nông sản xuất khẩu</v>
+      <c r="F4" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="1">
+        <v>46304</v>
+      </c>
+      <c r="J4" t="s">
+        <v>29</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>TRUCK</v>
-      </c>
-      <c r="B5" t="str">
-        <v>IMPORT</v>
-      </c>
-      <c r="C5" t="str">
-        <v>60C-888.99</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
+    <row r="5" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" t="s">
+        <v>25</v>
       </c>
       <c r="E5">
         <v>12500</v>
       </c>
-      <c r="F5" t="str">
-        <v>ĐỒNG NAI TRANS</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Phạm Quốc Dũng</v>
-      </c>
-      <c r="H5" t="str">
-        <v>0977112233</v>
-      </c>
-      <c r="I5" t="str">
-        <v>08/10/2026</v>
-      </c>
-      <c r="J5" t="str">
-        <v>Xe tải nặng 12.5 tấn nhận hàng sắt thép</v>
+      <c r="F5" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="1">
+        <v>46304</v>
+      </c>
+      <c r="J5" t="s">
+        <v>34</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>CONTAINER</v>
-      </c>
-      <c r="B6" t="str">
-        <v>IMPORT</v>
-      </c>
-      <c r="C6" t="str">
-        <v>15C-345.67</v>
-      </c>
-      <c r="D6" t="str">
-        <v>ONEU5544332</v>
+    <row r="6" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
       </c>
       <c r="E6">
         <v>26000</v>
       </c>
-      <c r="F6" t="str">
-        <v>HẢI PHÒNG MARITIME</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Vũ Đức Em</v>
-      </c>
-      <c r="H6" t="str">
-        <v>0933445566</v>
-      </c>
-      <c r="I6" t="str">
-        <v>08/10/2026</v>
-      </c>
-      <c r="J6" t="str">
-        <v>Cont đông lạnh nhập khẩu</v>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" s="1">
+        <v>46304</v>
+      </c>
+      <c r="J6" t="s">
+        <v>40</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>TRUCK</v>
-      </c>
-      <c r="B7" t="str">
-        <v>IMPORT</v>
-      </c>
-      <c r="C7" t="str">
-        <v>61C-456.78</v>
-      </c>
-      <c r="D7" t="str">
-        <v/>
+    <row r="7" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>25</v>
       </c>
       <c r="E7">
         <v>5200</v>
       </c>
-      <c r="F7" t="str">
-        <v>BÌNH DƯƠNG EXPRESS</v>
-      </c>
-      <c r="G7" t="str">
-        <v>Đỗ Hùng Giang</v>
-      </c>
-      <c r="H7" t="str">
-        <v>0966778899</v>
-      </c>
-      <c r="I7" t="str">
-        <v>08/10/2026</v>
-      </c>
-      <c r="J7" t="str">
-        <v>Xe tải nhẹ 5.2 tấn chở bao bì carton</v>
+      <c r="F7" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" s="1">
+        <v>46304</v>
+      </c>
+      <c r="J7" t="s">
+        <v>45</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>CONTAINER</v>
-      </c>
-      <c r="B8" t="str">
-        <v>EXPORT</v>
-      </c>
-      <c r="C8" t="str">
-        <v>51D-789.01</v>
-      </c>
-      <c r="D8" t="str">
-        <v>CMAU8877665</v>
+    <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s">
+        <v>17</v>
+      </c>
+      <c r="C8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
       </c>
       <c r="E8">
         <v>31000</v>
       </c>
-      <c r="F8" t="str">
-        <v>SAI GON SHIPLOG</v>
-      </c>
-      <c r="G8" t="str">
-        <v>Bùi Văn Hùng</v>
-      </c>
-      <c r="H8" t="str">
-        <v>0944556677</v>
-      </c>
-      <c r="I8" t="str">
-        <v>08/10/2026</v>
-      </c>
-      <c r="J8" t="str">
-        <v>Cont hạt điều xuất khẩu châu Âu</v>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>49</v>
+      </c>
+      <c r="H8" t="s">
+        <v>50</v>
+      </c>
+      <c r="I8" s="1">
+        <v>46304</v>
+      </c>
+      <c r="J8" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>TRUCK</v>
-      </c>
-      <c r="B9" t="str">
-        <v>EXPORT</v>
-      </c>
-      <c r="C9" t="str">
-        <v>72C-234.56</v>
-      </c>
-      <c r="D9" t="str">
-        <v/>
+    <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
       </c>
       <c r="E9">
         <v>15000</v>
       </c>
-      <c r="F9" t="str">
-        <v>VŨNG TÀU TRANSPORT</v>
-      </c>
-      <c r="G9" t="str">
-        <v>Ngô Đình Khôi</v>
-      </c>
-      <c r="H9" t="str">
-        <v>0922334455</v>
-      </c>
-      <c r="I9" t="str">
-        <v>08/10/2026</v>
-      </c>
-      <c r="J9" t="str">
-        <v>Xe tải 3 chân 15 tấn xuất hàng vật tư</v>
+      <c r="F9" t="s">
+        <v>53</v>
+      </c>
+      <c r="G9" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="1">
+        <v>46304</v>
+      </c>
+      <c r="J9" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J9"/>
+    <ignoredError sqref="A1:J1 A9:H9 A8:B8 D8:H8 A4:H7 A2:B2 J2 J9 J8 J3:J7 D2:H2 A3:B3 D3:H3" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>